--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_91_R10.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_91_R10.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>B. COLSON</t>
+          <t>T. HORTON TUCKER</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.4664</v>
+        <v>4.2358</v>
       </c>
       <c r="E2" t="n">
-        <v>3.7789</v>
+        <v>1.1179</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6876</v>
+        <v>3.1178</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.1785</v>
+        <v>3.986</v>
       </c>
       <c r="H2" t="n">
-        <v>1.287</v>
+        <v>-0.8522999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.4655</v>
+        <v>4.8383</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.8538</v>
+        <v>2.2102</v>
       </c>
       <c r="K2" t="n">
-        <v>1.3948</v>
+        <v>-1.1624</v>
       </c>
       <c r="L2" t="n">
-        <v>-2.2486</v>
+        <v>3.3726</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6753</v>
+        <v>1.7758</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1078</v>
+        <v>0.3101</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7831</v>
+        <v>1.4657</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9278</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9278</v>
+        <v>1.8556</v>
       </c>
       <c r="S2" t="n">
-        <v>0.217</v>
+        <v>-0.8946</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1325</v>
+        <v>-0.3811</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.9155</v>
+        <v>-0.5135</v>
       </c>
       <c r="V2" t="n">
-        <v>3.5002</v>
+        <v>1.6083</v>
       </c>
       <c r="W2" t="n">
-        <v>3.5002</v>
+        <v>1.6083</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T. HORTON TUCKER</t>
+          <t>B. COLSON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.7132</v>
+        <v>4.0783</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5282</v>
+        <v>3.1891</v>
       </c>
       <c r="F3" t="n">
-        <v>3.1851</v>
+        <v>0.8892</v>
       </c>
       <c r="G3" t="n">
-        <v>3.986</v>
+        <v>-0.1785</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.8522999999999999</v>
+        <v>1.287</v>
       </c>
       <c r="I3" t="n">
-        <v>4.8383</v>
+        <v>-1.4655</v>
       </c>
       <c r="J3" t="n">
-        <v>2.2102</v>
+        <v>-0.8538</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.1624</v>
+        <v>1.3948</v>
       </c>
       <c r="L3" t="n">
-        <v>3.3726</v>
+        <v>-2.2486</v>
       </c>
       <c r="M3" t="n">
-        <v>1.7758</v>
+        <v>0.6753</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3101</v>
+        <v>-0.1078</v>
       </c>
       <c r="O3" t="n">
-        <v>1.4657</v>
+        <v>0.7831</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8556</v>
+        <v>0.9278</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.4172</v>
+        <v>-0.1711</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9709</v>
+        <v>0.5427</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4463</v>
+        <v>-0.7139</v>
       </c>
       <c r="V3" t="n">
-        <v>1.6083</v>
+        <v>3.5002</v>
       </c>
       <c r="W3" t="n">
-        <v>1.6083</v>
+        <v>3.5002</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9715</v>
+        <v>3.0057</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8125</v>
+        <v>1.0484</v>
       </c>
       <c r="F4" t="n">
-        <v>2.159</v>
+        <v>1.9574</v>
       </c>
       <c r="G4" t="n">
         <v>5.4603</v>
@@ -766,13 +766,13 @@
         <v>1.6237</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.579</v>
+        <v>-0.5447</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0272</v>
+        <v>0.2087</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5517</v>
+        <v>-0.7534</v>
       </c>
       <c r="V4" t="n">
         <v>-1.214</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.9528</v>
+        <v>2.3301</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0539</v>
+        <v>1.7001</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8988</v>
+        <v>0.63</v>
       </c>
       <c r="G5" t="n">
         <v>1.434</v>
@@ -844,13 +844,13 @@
         <v>0.6959</v>
       </c>
       <c r="S5" t="n">
-        <v>2.1245</v>
+        <v>1.5017</v>
       </c>
       <c r="T5" t="n">
-        <v>1.2898</v>
+        <v>0.9359</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8347</v>
+        <v>0.5658</v>
       </c>
       <c r="V5" t="n">
         <v>-0.1418</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. BACOT JR.</t>
+          <t>W. BALDWIN IV</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4083</v>
+        <v>1.4294</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0569</v>
+        <v>-0.8245</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3515</v>
+        <v>2.254</v>
       </c>
       <c r="G6" t="n">
-        <v>2.0424</v>
+        <v>1.0134</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1585</v>
+        <v>-0.1443</v>
       </c>
       <c r="I6" t="n">
-        <v>1.8838</v>
+        <v>1.1577</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6593</v>
+        <v>0.0987</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0336</v>
+        <v>-0.4867</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6257</v>
+        <v>0.5854</v>
       </c>
       <c r="M6" t="n">
-        <v>1.3831</v>
+        <v>0.9147</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1249</v>
+        <v>0.3424</v>
       </c>
       <c r="O6" t="n">
-        <v>1.2582</v>
+        <v>0.5723</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.8556</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.3195</v>
+        <v>-3.4793</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4639</v>
+        <v>1.3917</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1494</v>
+        <v>0.8953</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6449</v>
+        <v>0.9478</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4955</v>
+        <v>-0.0525</v>
       </c>
       <c r="V6" t="n">
-        <v>1.0722</v>
+        <v>1.6083</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0722</v>
+        <v>1.6083</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>W. BALDWIN IV</t>
+          <t>K. BIRCH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3121</v>
+        <v>1.2155</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7066</v>
+        <v>1.5674</v>
       </c>
       <c r="F7" t="n">
-        <v>2.0187</v>
+        <v>-0.3519</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0134</v>
+        <v>3.5562</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1443</v>
+        <v>2.8033</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1577</v>
+        <v>0.7529</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0987</v>
+        <v>2.8095</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.4867</v>
+        <v>1.9998</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5854</v>
+        <v>0.8097</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9147</v>
+        <v>0.7467</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3424</v>
+        <v>0.8035</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5723</v>
+        <v>-0.0568</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.0876</v>
+        <v>0.6959</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3917</v>
+        <v>1.8556</v>
       </c>
       <c r="S7" t="n">
-        <v>0.778</v>
+        <v>-0.356</v>
       </c>
       <c r="T7" t="n">
-        <v>1.0657</v>
+        <v>-0.0824</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2877</v>
+        <v>-0.2737</v>
       </c>
       <c r="V7" t="n">
-        <v>1.6083</v>
+        <v>-2.6805</v>
       </c>
       <c r="W7" t="n">
-        <v>1.6083</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-2.6805</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. BIRCH</t>
+          <t>A. BACOT JR.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6929999999999999</v>
+        <v>1.1724</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9776</v>
+        <v>-0.179</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2847</v>
+        <v>1.3515</v>
       </c>
       <c r="G8" t="n">
-        <v>3.5562</v>
+        <v>2.0424</v>
       </c>
       <c r="H8" t="n">
-        <v>2.8033</v>
+        <v>0.1585</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7529</v>
+        <v>1.8838</v>
       </c>
       <c r="J8" t="n">
-        <v>2.8095</v>
+        <v>0.6593</v>
       </c>
       <c r="K8" t="n">
-        <v>1.9998</v>
+        <v>0.0336</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8097</v>
+        <v>0.6257</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7467</v>
+        <v>1.3831</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8035</v>
+        <v>0.1249</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0568</v>
+        <v>1.2582</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6959</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8556</v>
+        <v>0.4639</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8786</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6721</v>
+        <v>0.409</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2065</v>
+        <v>-0.4955</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.6805</v>
+        <v>1.0722</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.6805</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0113</v>
+        <v>-0.0956</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4856</v>
+        <v>-1.6035</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4743</v>
+        <v>1.5079</v>
       </c>
       <c r="G9" t="n">
         <v>0.5286</v>
@@ -1156,13 +1156,13 @@
         <v>1.1598</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5399</v>
+        <v>-0.6242</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3462</v>
+        <v>0.2282</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8861</v>
+        <v>-0.8525</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5033</v>
+        <v>-0.4697</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5033</v>
+        <v>-0.4697</v>
       </c>
       <c r="G10" t="n">
         <v>0.7863</v>
@@ -1234,13 +1234,13 @@
         <v>0.232</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4494</v>
+        <v>-0.4158</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4494</v>
+        <v>-0.4158</v>
       </c>
       <c r="V10" t="n">
         <v>-1.0722</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8507</v>
+        <v>-2.1202</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.6712</v>
+        <v>-1.9071</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1795</v>
+        <v>-0.2131</v>
       </c>
       <c r="G11" t="n">
         <v>3.0538</v>
@@ -1312,13 +1312,13 @@
         <v>1.1598</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3711</v>
+        <v>-1.6406</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0272</v>
+        <v>-0.2631</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.3438</v>
+        <v>-1.3774</v>
       </c>
       <c r="V11" t="n">
         <v>-1.214</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.8511</v>
+        <v>-5.4808</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.1022</v>
+        <v>-2.8663</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.7489</v>
+        <v>-2.6145</v>
       </c>
       <c r="G12" t="n">
         <v>0.2061</v>
@@ -1390,13 +1390,13 @@
         <v>0.232</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.217</v>
+        <v>0.1533</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0668</v>
+        <v>0.1691</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1502</v>
+        <v>-0.0158</v>
       </c>
       <c r="V12" t="n">
         <v>-3.7527</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.300900000000002</v>
+        <v>9.3009</v>
       </c>
       <c r="E13" t="n">
-        <v>1.242400000000001</v>
+        <v>1.2425</v>
       </c>
       <c r="F13" t="n">
-        <v>8.058600000000002</v>
+        <v>8.0586</v>
       </c>
       <c r="G13" t="n">
         <v>21.8886</v>
@@ -1468,13 +1468,13 @@
         <v>11.5978</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.1833</v>
+        <v>-2.1832</v>
       </c>
       <c r="T13" t="n">
-        <v>2.7149</v>
+        <v>2.714799999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.898</v>
+        <v>-4.898199999999999</v>
       </c>
       <c r="V13" t="n">
         <v>-2.286199999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.4071</v>
+        <v>5.3849</v>
       </c>
       <c r="E14" t="n">
-        <v>3.676</v>
+        <v>2.4965</v>
       </c>
       <c r="F14" t="n">
-        <v>2.7311</v>
+        <v>2.8884</v>
       </c>
       <c r="G14" t="n">
         <v>0.0478</v>
@@ -1546,13 +1546,13 @@
         <v>2.7834</v>
       </c>
       <c r="S14" t="n">
-        <v>2.4495</v>
+        <v>1.4273</v>
       </c>
       <c r="T14" t="n">
-        <v>2.5875</v>
+        <v>1.4079</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1379</v>
+        <v>0.0193</v>
       </c>
       <c r="V14" t="n">
         <v>2.2862</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. HOARD</t>
+          <t>W. RAYMAN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.1631</v>
+        <v>1.6365</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9751</v>
+        <v>1.8062</v>
       </c>
       <c r="F15" t="n">
-        <v>0.188</v>
+        <v>-0.1697</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.4366</v>
+        <v>1.6526</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.9281</v>
+        <v>-0.5558</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5085</v>
+        <v>2.2084</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.7675</v>
+        <v>1.3525</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.1589</v>
+        <v>0.1379</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3914</v>
+        <v>1.2146</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.6691</v>
+        <v>0.3001</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7692</v>
+        <v>-0.6938</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.8999</v>
+        <v>0.9939</v>
       </c>
       <c r="P15" t="n">
-        <v>2.5515</v>
+        <v>1.8556</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.5515</v>
+        <v>1.8556</v>
       </c>
       <c r="S15" t="n">
-        <v>2.5844</v>
+        <v>-0.2634</v>
       </c>
       <c r="T15" t="n">
-        <v>2.0647</v>
+        <v>-0.0824</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5197000000000001</v>
+        <v>-0.181</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.5361</v>
+        <v>-1.6083</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6778999999999999</v>
+        <v>0.5361</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.214</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>W. RAYMAN</t>
+          <t>J. HOARD</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6207</v>
+        <v>0.8498</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2165</v>
+        <v>1.0315</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5958</v>
+        <v>-0.1816</v>
       </c>
       <c r="G16" t="n">
-        <v>1.6526</v>
+        <v>-2.4366</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.5558</v>
+        <v>-1.9281</v>
       </c>
       <c r="I16" t="n">
-        <v>2.2084</v>
+        <v>-0.5085</v>
       </c>
       <c r="J16" t="n">
-        <v>1.3525</v>
+        <v>-0.7675</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1379</v>
+        <v>-1.1589</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2146</v>
+        <v>0.3914</v>
       </c>
       <c r="M16" t="n">
-        <v>0.3001</v>
+        <v>-1.6691</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6938</v>
+        <v>-0.7692</v>
       </c>
       <c r="O16" t="n">
-        <v>0.9939</v>
+        <v>-0.8999</v>
       </c>
       <c r="P16" t="n">
-        <v>1.8556</v>
+        <v>2.5515</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8556</v>
+        <v>2.5515</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.2792</v>
+        <v>1.2711</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6721</v>
+        <v>1.1211</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6071</v>
+        <v>0.15</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.6083</v>
+        <v>-0.5361</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5361</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.1444</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T. LEAF</t>
+          <t>T. BLATT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3877</v>
+        <v>0.7706</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5337</v>
+        <v>-0.961</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.146</v>
+        <v>1.7316</v>
       </c>
       <c r="G17" t="n">
-        <v>-3.7254</v>
+        <v>0.8707</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.8885</v>
+        <v>0.7971</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.8369</v>
+        <v>0.0736</v>
       </c>
       <c r="J17" t="n">
-        <v>-2.1744</v>
+        <v>0.8353</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.4985</v>
+        <v>2.0166</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6758999999999999</v>
+        <v>-1.1813</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.5509</v>
+        <v>0.0354</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.39</v>
+        <v>-1.2195</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.1609</v>
+        <v>1.2549</v>
       </c>
       <c r="P17" t="n">
+        <v>-0.6959</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-2.3195</v>
+      </c>
+      <c r="R17" t="n">
         <v>1.6237</v>
       </c>
-      <c r="Q17" t="n">
-        <v>-0.4639</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2.0876</v>
-      </c>
       <c r="S17" t="n">
-        <v>1.4172</v>
+        <v>0.5957</v>
       </c>
       <c r="T17" t="n">
-        <v>2.0998</v>
+        <v>0.5232</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6827</v>
+        <v>0.0725</v>
       </c>
       <c r="V17" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. LAVI</t>
+          <t>J. DIBARTOLOMEO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0835</v>
+        <v>0.4229</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2885</v>
+        <v>0.3914</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.205</v>
+        <v>0.0315</v>
       </c>
       <c r="G18" t="n">
-        <v>1.7441</v>
+        <v>-1.9654</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3421</v>
+        <v>-0.1284</v>
       </c>
       <c r="I18" t="n">
-        <v>1.402</v>
+        <v>-1.837</v>
       </c>
       <c r="J18" t="n">
-        <v>1.6619</v>
+        <v>-1.5223</v>
       </c>
       <c r="K18" t="n">
-        <v>0.521</v>
+        <v>0.0504</v>
       </c>
       <c r="L18" t="n">
-        <v>1.141</v>
+        <v>-1.5727</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0822</v>
+        <v>-0.4431</v>
       </c>
       <c r="N18" t="n">
         <v>-0.1788</v>
       </c>
       <c r="O18" t="n">
-        <v>0.261</v>
+        <v>-0.2643</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9801</v>
+        <v>0.8522</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3734</v>
+        <v>0.8415</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6067</v>
+        <v>0.0108</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.6083</v>
+        <v>1.0722</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. DIBARTOLOMEO</t>
+          <t>G. LAVI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0317</v>
+        <v>0.2744</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0375</v>
+        <v>1.2885</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0693</v>
+        <v>-1.0141</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.9654</v>
+        <v>1.7441</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1284</v>
+        <v>0.3421</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.837</v>
+        <v>1.402</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.5223</v>
+        <v>1.6619</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0504</v>
+        <v>0.521</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.5727</v>
+        <v>1.141</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4431</v>
+        <v>0.0822</v>
       </c>
       <c r="N19" t="n">
         <v>-0.1788</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2643</v>
+        <v>0.261</v>
       </c>
       <c r="P19" t="n">
-        <v>0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3976</v>
+        <v>-0.7892</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4876</v>
+        <v>-0.3734</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0901</v>
+        <v>-0.4158</v>
       </c>
       <c r="V19" t="n">
-        <v>1.0722</v>
+        <v>-1.6083</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>T. BLATT</t>
+          <t>M. SANTOS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1616</v>
+        <v>-0.1055</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6687</v>
+        <v>-0.4785</v>
       </c>
       <c r="F20" t="n">
-        <v>1.5071</v>
+        <v>0.373</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8707</v>
+        <v>0.1098</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7971</v>
+        <v>-0.1512</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0736</v>
+        <v>0.261</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8353</v>
+        <v>0.0168</v>
       </c>
       <c r="K20" t="n">
-        <v>2.0166</v>
+        <v>0.0168</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.1813</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0354</v>
+        <v>0.093</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.2195</v>
+        <v>-0.168</v>
       </c>
       <c r="O20" t="n">
-        <v>1.2549</v>
+        <v>0.261</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.6959</v>
+        <v>-0.232</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.3195</v>
+        <v>-0.4639</v>
       </c>
       <c r="R20" t="n">
-        <v>1.6237</v>
+        <v>0.232</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3365</v>
+        <v>0.0167</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1845</v>
+        <v>-0.0314</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.152</v>
+        <v>0.0481</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. SANTOS</t>
+          <t>T. LEAF</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2799</v>
+        <v>-0.646</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5965</v>
+        <v>-0.8817</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3166</v>
+        <v>0.2357</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1098</v>
+        <v>-3.7254</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1512</v>
+        <v>-1.8885</v>
       </c>
       <c r="I21" t="n">
-        <v>0.261</v>
+        <v>-1.8369</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0168</v>
+        <v>-2.1744</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0168</v>
+        <v>-1.4985</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>0.093</v>
+        <v>-1.5509</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.168</v>
+        <v>-0.39</v>
       </c>
       <c r="O21" t="n">
-        <v>0.261</v>
+        <v>-1.1609</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.232</v>
+        <v>1.6237</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.4639</v>
       </c>
       <c r="R21" t="n">
-        <v>0.232</v>
+        <v>2.0876</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1577</v>
+        <v>0.3835</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1494</v>
+        <v>0.6844</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0083</v>
+        <v>-0.3009</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>L. WALKER IV</t>
+          <t>J. DOWTIN JR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4121</v>
+        <v>-2.093</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.4614</v>
+        <v>-2.9735</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0494</v>
+        <v>0.8804999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>-5.2926</v>
+        <v>-3.0098</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.1273</v>
+        <v>-2.7757</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.1654</v>
+        <v>-0.2341</v>
       </c>
       <c r="J22" t="n">
-        <v>-3.5553</v>
+        <v>-3.1278</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.2331</v>
+        <v>-2.2176</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.3222</v>
+        <v>-0.9102</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.7373</v>
+        <v>0.118</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8942</v>
+        <v>-0.5581</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.8431</v>
+        <v>0.6761</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.5515</v>
+        <v>-1.6237</v>
       </c>
       <c r="R22" t="n">
-        <v>1.6237</v>
+        <v>2.3195</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1278</v>
+        <v>-0.4569</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0351</v>
+        <v>0.0279</v>
       </c>
       <c r="U22" t="n">
-        <v>0.163</v>
+        <v>-0.4848</v>
       </c>
       <c r="V22" t="n">
-        <v>2.6805</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W22" t="n">
-        <v>2.6805</v>
+        <v>1.7501</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. DOWTIN JR</t>
+          <t>L. WALKER IV</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.0746</v>
+        <v>-3.3442</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.271</v>
+        <v>-3.2255</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1963</v>
+        <v>-0.1187</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.0098</v>
+        <v>-5.2926</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.7757</v>
+        <v>-2.1273</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2341</v>
+        <v>-3.1654</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.1278</v>
+        <v>-3.5553</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.2176</v>
+        <v>-1.2331</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.9102</v>
+        <v>-2.3222</v>
       </c>
       <c r="M23" t="n">
-        <v>0.118</v>
+        <v>-1.7373</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.5581</v>
+        <v>-0.8942</v>
       </c>
       <c r="O23" t="n">
-        <v>0.6761</v>
+        <v>-0.8431</v>
       </c>
       <c r="P23" t="n">
-        <v>0.6959</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.6237</v>
+        <v>-2.5515</v>
       </c>
       <c r="R23" t="n">
-        <v>2.3195</v>
+        <v>1.6237</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.4386</v>
+        <v>0.1957</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.2696</v>
+        <v>0.2008</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.169</v>
+        <v>-0.005</v>
       </c>
       <c r="V23" t="n">
-        <v>0.6778999999999999</v>
+        <v>2.6805</v>
       </c>
       <c r="W23" t="n">
-        <v>1.7501</v>
+        <v>2.6805</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. CLARK III</t>
+          <t>O. BRISSETT</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.1297</v>
+        <v>-5.3166</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.9438</v>
+        <v>-5.091</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.1859</v>
+        <v>-0.2256</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.4912</v>
+        <v>-5.3926</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0025</v>
+        <v>-2.8296</v>
       </c>
       <c r="I24" t="n">
-        <v>-4.4937</v>
+        <v>-2.563</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.0046</v>
+        <v>-3.2553</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0672</v>
+        <v>-2.2715</v>
       </c>
       <c r="L24" t="n">
-        <v>-3.0718</v>
+        <v>-0.9838</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.4866</v>
+        <v>-2.1373</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.06469999999999999</v>
+        <v>-0.5581</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.422</v>
+        <v>-1.5792</v>
       </c>
       <c r="P24" t="n">
-        <v>1.6237</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.4639</v>
+        <v>-2.5515</v>
       </c>
       <c r="R24" t="n">
-        <v>2.0876</v>
+        <v>1.1598</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1177</v>
+        <v>1.0734</v>
       </c>
       <c r="T24" t="n">
-        <v>0.4525</v>
+        <v>0.7158</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5702</v>
+        <v>0.3576</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.1444</v>
+        <v>0.3943</v>
       </c>
       <c r="W24" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-3.2166</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>O. BRISSETT</t>
+          <t>J. CLARK III</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.8734</v>
+        <v>-5.5622</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.9166</v>
+        <v>-2.5335</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0432</v>
+        <v>-3.0286</v>
       </c>
       <c r="G25" t="n">
-        <v>-5.3926</v>
+        <v>-4.4912</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.8296</v>
+        <v>0.0025</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.563</v>
+        <v>-4.4937</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.2553</v>
+        <v>-3.0046</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.2715</v>
+        <v>0.0672</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.9838</v>
+        <v>-3.0718</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.1373</v>
+        <v>-1.4866</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.5581</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.5792</v>
+        <v>-1.422</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.5515</v>
+        <v>-0.4639</v>
       </c>
       <c r="R25" t="n">
-        <v>1.1598</v>
+        <v>2.0876</v>
       </c>
       <c r="S25" t="n">
-        <v>0.5165999999999999</v>
+        <v>-0.5502</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1098</v>
+        <v>-0.1373</v>
       </c>
       <c r="U25" t="n">
-        <v>0.6264</v>
+        <v>-0.4129</v>
       </c>
       <c r="V25" t="n">
-        <v>0.3943</v>
+        <v>-2.1444</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X25" t="n">
-        <v>0.3943</v>
+        <v>-3.2166</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-9.3009</v>
+        <v>-7.7284</v>
       </c>
       <c r="E26" t="n">
-        <v>-9.130699999999997</v>
+        <v>-9.130600000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.1703000000000002</v>
+        <v>1.4024</v>
       </c>
       <c r="G26" t="n">
         <v>-21.8886</v>
@@ -2452,7 +2452,7 @@
         <v>-12.4199</v>
       </c>
       <c r="I26" t="n">
-        <v>-9.4689</v>
+        <v>-9.468899999999998</v>
       </c>
       <c r="J26" t="n">
         <v>-13.5786</v>
@@ -2461,10 +2461,10 @@
         <v>-5.999000000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>-7.579500000000001</v>
+        <v>-7.579499999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>-8.309900000000001</v>
+        <v>-8.309899999999999</v>
       </c>
       <c r="N26" t="n">
         <v>-6.4209</v>
@@ -2473,7 +2473,7 @@
         <v>-1.8892</v>
       </c>
       <c r="P26" t="n">
-        <v>8.118400000000001</v>
+        <v>8.118399999999999</v>
       </c>
       <c r="Q26" t="n">
         <v>-11.5977</v>
@@ -2482,13 +2482,13 @@
         <v>19.7161</v>
       </c>
       <c r="S26" t="n">
-        <v>2.1833</v>
+        <v>3.7559</v>
       </c>
       <c r="T26" t="n">
-        <v>4.8982</v>
+        <v>4.898099999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>-2.7149</v>
+        <v>-1.1421</v>
       </c>
       <c r="V26" t="n">
         <v>2.2862</v>
